--- a/_docs/grades.xlsx
+++ b/_docs/grades.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kruppajo/work/GitHub/archive/_docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6AF4F5D-64A4-F84D-BBA6-CE1EE34262E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14A5A186-6EC7-834D-9122-78EB0E64CD74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="920" yWindow="1940" windowWidth="21080" windowHeight="15280" xr2:uid="{56F68AFB-79FC-2E48-BB60-E7104B640CA5}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1875" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1895" uniqueCount="13">
   <si>
     <t>year</t>
   </si>
@@ -72,6 +72,9 @@
   </si>
   <si>
     <t>2024/25</t>
+  </si>
+  <si>
+    <t>2025/26</t>
   </si>
 </sst>
 </file>
@@ -435,7 +438,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7920AA11-A75E-2E45-9C61-C279847E759F}">
-  <dimension ref="A1:C1136"/>
+  <dimension ref="A1:C1146"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="39.83203125" bestFit="1" customWidth="1"/>
@@ -12937,8 +12940,119 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
+    <row r="1137" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1137" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1137" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1137">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1138" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1138" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1138" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1138">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1139" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1139" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1139" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1139">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1140" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1140" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1140" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1140">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1141" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1141" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1141" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1141">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="1142" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1142" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1142" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1142">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="1143" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1143" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1143" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1143">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="1144" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1144" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1144" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1144">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="1145" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1145" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1145" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1145">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="1146" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1146" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1146" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1146">
+        <v>1.7</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/_docs/grades.xlsx
+++ b/_docs/grades.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kruppajo/work/GitHub/archive/_docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14A5A186-6EC7-834D-9122-78EB0E64CD74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6328ECDE-295E-EA42-BDCF-47BA2834910F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="920" yWindow="1940" windowWidth="21080" windowHeight="15280" xr2:uid="{56F68AFB-79FC-2E48-BB60-E7104B640CA5}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1895" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1933" uniqueCount="13">
   <si>
     <t>year</t>
   </si>
@@ -81,7 +81,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -99,6 +99,12 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -121,9 +127,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -438,7 +445,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7920AA11-A75E-2E45-9C61-C279847E759F}">
-  <dimension ref="A1:C1146"/>
+  <dimension ref="A1:C1165"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="39.83203125" bestFit="1" customWidth="1"/>
@@ -13050,6 +13057,215 @@
         <v>1.7</v>
       </c>
     </row>
+    <row r="1147" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1147" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1147" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1147" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1148" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1148" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1148" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1148" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1149" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1149" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1149" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1149" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1150" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1150" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1150" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1150" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1151" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1151" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1151" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1151" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1152" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1152" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1152" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1152" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1153" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1153" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1153" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1153" s="2">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="1154" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1154" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1154" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1154" s="2">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="1155" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1155" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1155" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1155" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1156" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1156" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1156" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1156" s="2">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="1157" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1157" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1157" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1157" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1158" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1158" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1158" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1158" s="2">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="1159" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1159" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1159" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1159" s="2">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="1160" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1160" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1160" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1160" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1161" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1161" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1161" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1161" s="2">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="1162" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1162" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1162" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1162" s="2">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="1163" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1163" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1163" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1163" s="2">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="1164" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1164" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1164" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1164" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1165" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1165" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1165" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1165" s="2">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>

--- a/_docs/grades.xlsx
+++ b/_docs/grades.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kruppajo/work/GitHub/archive/_docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6328ECDE-295E-EA42-BDCF-47BA2834910F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C98190E5-2202-F849-BDCA-BC22B0DCAC0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="920" yWindow="1940" windowWidth="21080" windowHeight="15280" xr2:uid="{56F68AFB-79FC-2E48-BB60-E7104B640CA5}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1933" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2295" uniqueCount="13">
   <si>
     <t>year</t>
   </si>
@@ -445,7 +445,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7920AA11-A75E-2E45-9C61-C279847E759F}">
-  <dimension ref="A1:C1165"/>
+  <dimension ref="A1:C1346"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="39.83203125" bestFit="1" customWidth="1"/>
@@ -13262,8 +13262,1999 @@
       <c r="B1165" t="s">
         <v>7</v>
       </c>
-      <c r="C1165" s="2">
-        <v>5</v>
+      <c r="C1165">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="1166" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1166" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1166" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1166">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="1167" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1167" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1167" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1167">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1168" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1168" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1168" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1168">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="1169" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1169" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1169" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1169">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1170" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1170" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1170" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1170">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1171" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1171" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1171" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1171">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1172" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1172" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1172" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1172">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1173" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1173" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1173" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1173">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="1174" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1174" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1174" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1174">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1175" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1175" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1175" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1175">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="1176" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1176" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1176" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1176">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1177" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1177" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1177" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1177">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="1178" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1178" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1178" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1178">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="1179" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1179" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1179" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1179">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="1180" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1180" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1180" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1180">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1181" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1181" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1181" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1181">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="1182" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1182" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1182" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1182">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="1183" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1183" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1183" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1183">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="1184" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1184" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1184" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1184">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="1185" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1185" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1185" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1185">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="1186" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1186" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1186" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1186">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1187" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1187" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1187" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1187">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1188" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1188" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1188" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1188">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="1189" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1189" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1189" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1189">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="1190" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1190" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1190" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1190">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1191" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1191" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1191" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1191">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1192" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1192" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1192" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1192">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="1193" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1193" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1193" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1193">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="1194" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1194" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1194" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1194">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1195" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1195" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1195" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1195">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="1196" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1196" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1196" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1196">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="1197" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1197" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1197" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1197">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="1198" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1198" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1198" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1198">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1199" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1199" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1199" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1199">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1200" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1200" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1200" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1200">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1201" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1201" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1201" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1201">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="1202" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1202" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1202" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1202">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1203" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1203" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1203" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1203">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1204" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1204" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1204" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1204">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1205" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1205" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1205" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1205">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="1206" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1206" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1206" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1206">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="1207" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1207" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1207" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1207">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="1208" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1208" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1208" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1208">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="1209" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1209" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1209" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1209">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1210" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1210" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1210" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1210">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="1211" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1211" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1211" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1211">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="1212" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1212" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1212" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1212">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1213" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1213" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1213" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1213">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1214" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1214" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1214" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1214">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1215" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1215" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1215" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1215">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1216" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1216" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1216" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1216">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="1217" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1217" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1217" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1217">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="1218" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1218" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1218" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1218">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="1219" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1219" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1219" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1219">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="1220" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1220" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1220" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1220">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="1221" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1221" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1221" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1221">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="1222" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1222" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1222" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1222">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="1223" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1223" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1223" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1223">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1224" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1224" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1224" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1224">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1225" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1225" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1225" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1225">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="1226" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1226" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1226" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1226">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="1227" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1227" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1227" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1227">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="1228" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1228" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1228" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1228">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="1229" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1229" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1229" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1229">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="1230" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1230" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1230" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1230">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="1231" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1231" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1231" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1231">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="1232" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1232" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1232" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1232">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="1233" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1233" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1233" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1233">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="1234" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1234" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1234" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1234">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="1235" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1235" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1235" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1235">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="1236" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1236" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1236" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1236">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1237" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1237" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1237" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1237">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1238" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1238" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1238" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1238">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1239" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1239" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1239" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1239">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="1240" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1240" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1240" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1240">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1241" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1241" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1241" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1241">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1242" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1242" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1242" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1242">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1243" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1243" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1243" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1243">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="1244" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1244" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1244" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1244">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="1245" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1245" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1245" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1245">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="1246" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1246" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1246" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1246">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1247" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1247" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1247" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1247">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="1248" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1248" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1248" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1248">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="1249" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1249" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1249" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1249">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="1250" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1250" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1250" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1250">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="1251" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1251" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1251" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1251">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="1252" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1252" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1252" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1252">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="1253" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1253" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1253" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1253">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="1254" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1254" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1254" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1254">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="1255" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1255" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1255" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1255">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1256" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1256" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1256" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1256">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="1257" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1257" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1257" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1257">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="1258" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1258" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1258" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1258">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1259" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1259" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1259" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1259">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1260" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1260" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1260" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1260">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1261" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1261" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1261" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1261">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1262" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1262" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1262" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1262">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="1263" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1263" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1263" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1263">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1264" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1264" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1264" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1264">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="1265" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1265" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1265" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1265">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1266" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1266" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1266" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1266">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1267" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1267" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1267" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1267">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1268" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1268" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1268" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1268">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1269" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1269" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1269" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1269">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="1270" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1270" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1270" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1270">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="1271" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1271" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1271" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1271">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1272" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1272" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1272" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1272">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1273" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1273" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1273" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1273">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1274" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1274" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1274" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1274">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1275" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1275" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1275" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1275">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="1276" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1276" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1276" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1276">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="1277" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1277" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1277" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1277">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1278" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1278" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1278" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1278">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1279" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1279" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1279" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1279">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="1280" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1280" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1280" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1280">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1281" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1281" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1281" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1281">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="1282" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1282" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1282" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1282">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1283" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1283" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1283" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1283">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1284" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1284" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1284" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1284">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1285" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1285" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1285" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1285">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="1286" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1286" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1286" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1286">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="1287" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1287" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1287" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1287">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1288" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1288" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1288" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1288">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="1289" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1289" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1289" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1289">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1290" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1290" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1290" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1290">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="1291" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1291" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1291" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1291">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1292" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1292" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1292" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1292">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="1293" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1293" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1293" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1293">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="1294" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1294" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1294" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1294">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="1295" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1295" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1295" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1295">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="1296" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1296" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1296" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1296">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="1297" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1297" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1297" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1297">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="1298" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1298" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1298" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1298">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="1299" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1299" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1299" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1299">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="1300" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1300" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1300" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1300">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="1301" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1301" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1301" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1301">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1302" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1302" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1302" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1302">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="1303" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1303" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1303" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1303">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="1304" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1304" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1304" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1304">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="1305" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1305" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1305" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1305">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="1306" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1306" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1306" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1306">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="1307" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1307" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1307" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1307">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="1308" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1308" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1308" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1308">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1309" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1309" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1309" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1309">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1310" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1310" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1310" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1310">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="1311" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1311" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1311" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1311">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1312" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1312" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1312" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1312">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1313" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1313" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1313" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1313">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1314" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1314" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1314" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1314">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="1315" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1315" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1315" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1315">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1316" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1316" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1316" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1316">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1317" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1317" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1317" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1317">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="1318" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1318" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1318" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1318">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="1319" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1319" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1319" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1319">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="1320" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1320" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1320" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1320">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="1321" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1321" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1321" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1321">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="1322" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1322" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1322" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1322">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="1323" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1323" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1323" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1323">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1324" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1324" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1324" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1324">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="1325" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1325" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1325" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1325">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1326" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1326" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1326" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1326">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="1327" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1327" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1327" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1327">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1328" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1328" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1328" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1328">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1329" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1329" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1329" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1329">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1330" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1330" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1330" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1330">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="1331" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1331" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1331" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1331">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="1332" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1332" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1332" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1332">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1333" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1333" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1333" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1333">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1334" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1334" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1334" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1334">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="1335" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1335" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1335" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1335">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1336" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1336" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1336" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1336">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1337" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1337" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1337" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1337">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="1338" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1338" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1338" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1338">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1339" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1339" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1339" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1339">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="1340" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1340" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1340" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1340">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="1341" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1341" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1341" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1341">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="1342" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1342" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1342" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1342">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="1343" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1343" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1343" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1343">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="1344" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1344" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1344" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1344">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1345" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1345" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1345" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1345">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1346" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1346" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1346" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1346">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/_docs/grades.xlsx
+++ b/_docs/grades.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kruppajo/work/GitHub/archive/_docs/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jokruppa/GitHub/archive/_docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C98190E5-2202-F849-BDCA-BC22B0DCAC0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3001589-F054-0F43-8A21-18143930E1D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="920" yWindow="1940" windowWidth="21080" windowHeight="15280" xr2:uid="{56F68AFB-79FC-2E48-BB60-E7104B640CA5}"/>
+    <workbookView xWindow="6500" yWindow="1700" windowWidth="21080" windowHeight="15280" xr2:uid="{56F68AFB-79FC-2E48-BB60-E7104B640CA5}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2295" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2314" uniqueCount="13">
   <si>
     <t>year</t>
   </si>
@@ -445,7 +445,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7920AA11-A75E-2E45-9C61-C279847E759F}">
-  <dimension ref="A1:C1346"/>
+  <dimension ref="A1:C1365"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="39.83203125" bestFit="1" customWidth="1"/>
@@ -15257,6 +15257,215 @@
         <v>1</v>
       </c>
     </row>
+    <row r="1347" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1347">
+        <v>2026</v>
+      </c>
+      <c r="B1347" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1347">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="1348" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1348">
+        <v>2026</v>
+      </c>
+      <c r="B1348" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1348">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="1349" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1349">
+        <v>2026</v>
+      </c>
+      <c r="B1349" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1349">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1350" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1350">
+        <v>2026</v>
+      </c>
+      <c r="B1350" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1350">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="1351" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1351">
+        <v>2026</v>
+      </c>
+      <c r="B1351" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1351">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="1352" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1352">
+        <v>2026</v>
+      </c>
+      <c r="B1352" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1352">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="1353" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1353">
+        <v>2026</v>
+      </c>
+      <c r="B1353" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1353">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="1354" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1354">
+        <v>2026</v>
+      </c>
+      <c r="B1354" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1354">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1355" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1355">
+        <v>2026</v>
+      </c>
+      <c r="B1355" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1355">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1356" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1356">
+        <v>2026</v>
+      </c>
+      <c r="B1356" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1356">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="1357" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1357">
+        <v>2026</v>
+      </c>
+      <c r="B1357" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1357">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="1358" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1358">
+        <v>2026</v>
+      </c>
+      <c r="B1358" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1358">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="1359" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1359">
+        <v>2026</v>
+      </c>
+      <c r="B1359" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1359">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="1360" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1360">
+        <v>2026</v>
+      </c>
+      <c r="B1360" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1360">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="1361" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1361">
+        <v>2026</v>
+      </c>
+      <c r="B1361" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1361">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="1362" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1362">
+        <v>2026</v>
+      </c>
+      <c r="B1362" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1362">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="1363" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1363">
+        <v>2026</v>
+      </c>
+      <c r="B1363" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1363">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1364" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1364">
+        <v>2026</v>
+      </c>
+      <c r="B1364" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1364">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="1365" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1365">
+        <v>2026</v>
+      </c>
+      <c r="B1365" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1365">
+        <v>1.7</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>

--- a/_docs/grades.xlsx
+++ b/_docs/grades.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jokruppa/GitHub/archive/_docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3001589-F054-0F43-8A21-18143930E1D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0DA636E-5452-B24E-B99F-D82F0D839622}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6500" yWindow="1700" windowWidth="21080" windowHeight="15280" xr2:uid="{56F68AFB-79FC-2E48-BB60-E7104B640CA5}"/>
+    <workbookView xWindow="22800" yWindow="3200" windowWidth="21080" windowHeight="15280" xr2:uid="{56F68AFB-79FC-2E48-BB60-E7104B640CA5}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2314" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2377" uniqueCount="13">
   <si>
     <t>year</t>
   </si>
@@ -445,7 +445,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7920AA11-A75E-2E45-9C61-C279847E759F}">
-  <dimension ref="A1:C1365"/>
+  <dimension ref="A1:C1428"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="39.83203125" bestFit="1" customWidth="1"/>
@@ -15466,6 +15466,699 @@
         <v>1.7</v>
       </c>
     </row>
+    <row r="1366" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1366">
+        <v>2026</v>
+      </c>
+      <c r="B1366" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1366">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="1367" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1367">
+        <v>2026</v>
+      </c>
+      <c r="B1367" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1367">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="1368" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1368">
+        <v>2026</v>
+      </c>
+      <c r="B1368" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1368">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1369" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1369">
+        <v>2026</v>
+      </c>
+      <c r="B1369" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1369">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1370" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1370">
+        <v>2026</v>
+      </c>
+      <c r="B1370" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1370">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1371" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1371">
+        <v>2026</v>
+      </c>
+      <c r="B1371" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1371">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="1372" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1372">
+        <v>2026</v>
+      </c>
+      <c r="B1372" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1372">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="1373" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1373">
+        <v>2026</v>
+      </c>
+      <c r="B1373" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1373">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="1374" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1374">
+        <v>2026</v>
+      </c>
+      <c r="B1374" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1374">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1375" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1375">
+        <v>2026</v>
+      </c>
+      <c r="B1375" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1375">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="1376" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1376">
+        <v>2026</v>
+      </c>
+      <c r="B1376" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1376">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="1377" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1377">
+        <v>2026</v>
+      </c>
+      <c r="B1377" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1377">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1378" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1378">
+        <v>2026</v>
+      </c>
+      <c r="B1378" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1378">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="1379" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1379">
+        <v>2026</v>
+      </c>
+      <c r="B1379" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1379">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="1380" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1380">
+        <v>2026</v>
+      </c>
+      <c r="B1380" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1380">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1381" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1381">
+        <v>2026</v>
+      </c>
+      <c r="B1381" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1381">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1382" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1382">
+        <v>2026</v>
+      </c>
+      <c r="B1382" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1382">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="1383" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1383">
+        <v>2026</v>
+      </c>
+      <c r="B1383" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1383">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="1384" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1384">
+        <v>2026</v>
+      </c>
+      <c r="B1384" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1384">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1385" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1385">
+        <v>2026</v>
+      </c>
+      <c r="B1385" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1385">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="1386" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1386">
+        <v>2026</v>
+      </c>
+      <c r="B1386" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1386">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1387" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1387">
+        <v>2026</v>
+      </c>
+      <c r="B1387" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1387">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="1388" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1388">
+        <v>2026</v>
+      </c>
+      <c r="B1388" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1388">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="1389" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1389">
+        <v>2026</v>
+      </c>
+      <c r="B1389" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1389">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1390" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1390">
+        <v>2026</v>
+      </c>
+      <c r="B1390" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1390">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="1391" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1391">
+        <v>2026</v>
+      </c>
+      <c r="B1391" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1391">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="1392" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1392">
+        <v>2026</v>
+      </c>
+      <c r="B1392" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1392">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="1393" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1393">
+        <v>2026</v>
+      </c>
+      <c r="B1393" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1393">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1394" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1394">
+        <v>2026</v>
+      </c>
+      <c r="B1394" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1394">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="1395" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1395">
+        <v>2026</v>
+      </c>
+      <c r="B1395" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1395">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="1396" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1396">
+        <v>2026</v>
+      </c>
+      <c r="B1396" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1396">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="1397" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1397">
+        <v>2026</v>
+      </c>
+      <c r="B1397" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1397">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1398" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1398">
+        <v>2026</v>
+      </c>
+      <c r="B1398" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1398">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1399" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1399">
+        <v>2026</v>
+      </c>
+      <c r="B1399" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1399">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="1400" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1400">
+        <v>2026</v>
+      </c>
+      <c r="B1400" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1400">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="1401" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1401">
+        <v>2026</v>
+      </c>
+      <c r="B1401" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1401">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="1402" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1402">
+        <v>2026</v>
+      </c>
+      <c r="B1402" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1402">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="1403" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1403">
+        <v>2026</v>
+      </c>
+      <c r="B1403" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1403">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="1404" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1404">
+        <v>2026</v>
+      </c>
+      <c r="B1404" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1404">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1405" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1405">
+        <v>2026</v>
+      </c>
+      <c r="B1405" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1405">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="1406" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1406">
+        <v>2026</v>
+      </c>
+      <c r="B1406" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1406">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="1407" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1407">
+        <v>2026</v>
+      </c>
+      <c r="B1407" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1407">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="1408" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1408">
+        <v>2026</v>
+      </c>
+      <c r="B1408" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1408">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1409" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1409">
+        <v>2026</v>
+      </c>
+      <c r="B1409" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1409">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="1410" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1410">
+        <v>2026</v>
+      </c>
+      <c r="B1410" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1410">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1411" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1411">
+        <v>2026</v>
+      </c>
+      <c r="B1411" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1411">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="1412" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1412">
+        <v>2026</v>
+      </c>
+      <c r="B1412" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1412">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1413" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1413">
+        <v>2026</v>
+      </c>
+      <c r="B1413" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1413">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1414" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1414">
+        <v>2026</v>
+      </c>
+      <c r="B1414" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1414">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="1415" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1415">
+        <v>2026</v>
+      </c>
+      <c r="B1415" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1415">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1416" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1416">
+        <v>2026</v>
+      </c>
+      <c r="B1416" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1416">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="1417" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1417">
+        <v>2026</v>
+      </c>
+      <c r="B1417" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1417">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="1418" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1418">
+        <v>2026</v>
+      </c>
+      <c r="B1418" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1418">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1419" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1419">
+        <v>2026</v>
+      </c>
+      <c r="B1419" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1419">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="1420" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1420">
+        <v>2026</v>
+      </c>
+      <c r="B1420" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1420">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1421" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1421">
+        <v>2026</v>
+      </c>
+      <c r="B1421" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1421">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1422" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1422">
+        <v>2026</v>
+      </c>
+      <c r="B1422" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1422">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="1423" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1423">
+        <v>2026</v>
+      </c>
+      <c r="B1423" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1423">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="1424" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1424">
+        <v>2026</v>
+      </c>
+      <c r="B1424" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1424">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="1425" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1425">
+        <v>2026</v>
+      </c>
+      <c r="B1425" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1425">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="1426" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1426">
+        <v>2026</v>
+      </c>
+      <c r="B1426" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1426">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="1427" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1427">
+        <v>2026</v>
+      </c>
+      <c r="B1427" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1427">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="1428" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1428">
+        <v>2026</v>
+      </c>
+      <c r="B1428" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1428">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>

--- a/_docs/grades.xlsx
+++ b/_docs/grades.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jokruppa/GitHub/archive/_docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0DA636E-5452-B24E-B99F-D82F0D839622}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81C15390-F065-6549-95CB-D868545E2541}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22800" yWindow="3200" windowWidth="21080" windowHeight="15280" xr2:uid="{56F68AFB-79FC-2E48-BB60-E7104B640CA5}"/>
+    <workbookView xWindow="20540" yWindow="3200" windowWidth="21080" windowHeight="15280" xr2:uid="{56F68AFB-79FC-2E48-BB60-E7104B640CA5}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2377" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2388" uniqueCount="14">
   <si>
     <t>year</t>
   </si>
@@ -75,6 +75,9 @@
   </si>
   <si>
     <t>2025/26</t>
+  </si>
+  <si>
+    <t>Modellierung landwirtschaftlicher Daten</t>
   </si>
 </sst>
 </file>
@@ -445,7 +448,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7920AA11-A75E-2E45-9C61-C279847E759F}">
-  <dimension ref="A1:C1428"/>
+  <dimension ref="A1:C1439"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="39.83203125" bestFit="1" customWidth="1"/>
@@ -16153,9 +16156,130 @@
         <v>2026</v>
       </c>
       <c r="B1428" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C1428">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="1429" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1429">
+        <v>2026</v>
+      </c>
+      <c r="B1429" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1429">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1430" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1430">
+        <v>2026</v>
+      </c>
+      <c r="B1430" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1430">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="1431" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1431">
+        <v>2026</v>
+      </c>
+      <c r="B1431" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1431">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="1432" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1432">
+        <v>2026</v>
+      </c>
+      <c r="B1432" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1432">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1433" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1433">
+        <v>2026</v>
+      </c>
+      <c r="B1433" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1433">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="1434" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1434">
+        <v>2026</v>
+      </c>
+      <c r="B1434" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1434">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="1435" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1435">
+        <v>2026</v>
+      </c>
+      <c r="B1435" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1435">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1436" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1436">
+        <v>2026</v>
+      </c>
+      <c r="B1436" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1436">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1437" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1437">
+        <v>2026</v>
+      </c>
+      <c r="B1437" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1437">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="1438" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1438">
+        <v>2026</v>
+      </c>
+      <c r="B1438" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1438">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="1439" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1439">
+        <v>2026</v>
+      </c>
+      <c r="B1439" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1439">
         <v>5</v>
       </c>
     </row>

--- a/_docs/grades.xlsx
+++ b/_docs/grades.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jokruppa/GitHub/archive/_docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81C15390-F065-6549-95CB-D868545E2541}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06325B40-A6EA-3B4B-A052-8439283B6844}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20540" yWindow="3200" windowWidth="21080" windowHeight="15280" xr2:uid="{56F68AFB-79FC-2E48-BB60-E7104B640CA5}"/>
+    <workbookView xWindow="17320" yWindow="3200" windowWidth="21080" windowHeight="15280" xr2:uid="{56F68AFB-79FC-2E48-BB60-E7104B640CA5}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2388" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2403" uniqueCount="15">
   <si>
     <t>year</t>
   </si>
@@ -78,6 +78,9 @@
   </si>
   <si>
     <t>Modellierung landwirtschaftlicher Daten</t>
+  </si>
+  <si>
+    <t>Angewandte Mathematik und Statistik</t>
   </si>
 </sst>
 </file>
@@ -448,7 +451,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7920AA11-A75E-2E45-9C61-C279847E759F}">
-  <dimension ref="A1:C1439"/>
+  <dimension ref="A1:C1454"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="39.83203125" bestFit="1" customWidth="1"/>
@@ -16283,6 +16286,171 @@
         <v>5</v>
       </c>
     </row>
+    <row r="1440" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1440">
+        <v>2026</v>
+      </c>
+      <c r="B1440" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1440">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="1441" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1441">
+        <v>2026</v>
+      </c>
+      <c r="B1441" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1441">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="1442" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1442">
+        <v>2026</v>
+      </c>
+      <c r="B1442" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1442">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1443" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1443">
+        <v>2026</v>
+      </c>
+      <c r="B1443" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1443">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="1444" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1444">
+        <v>2026</v>
+      </c>
+      <c r="B1444" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1444">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="1445" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1445">
+        <v>2026</v>
+      </c>
+      <c r="B1445" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1445">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="1446" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1446">
+        <v>2026</v>
+      </c>
+      <c r="B1446" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1446">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="1447" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1447">
+        <v>2026</v>
+      </c>
+      <c r="B1447" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1447">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="1448" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1448">
+        <v>2026</v>
+      </c>
+      <c r="B1448" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1448">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1449" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1449">
+        <v>2026</v>
+      </c>
+      <c r="B1449" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1449">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="1450" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1450">
+        <v>2026</v>
+      </c>
+      <c r="B1450" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1450">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="1451" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1451">
+        <v>2026</v>
+      </c>
+      <c r="B1451" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1451">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="1452" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1452">
+        <v>2026</v>
+      </c>
+      <c r="B1452" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1452">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1453" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1453">
+        <v>2026</v>
+      </c>
+      <c r="B1453" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1453">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1454" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1454">
+        <v>2026</v>
+      </c>
+      <c r="B1454" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1454">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
